--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +854,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +915,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +935,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -965,32 +973,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1034,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1054,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1092,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1133,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2856,1006 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -864,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -891,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -930,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -973,36 +989,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1010,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1034,37 +1046,33 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>174.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1441,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1474,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1696,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1918,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2275,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2386,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2608,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2719,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2941,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3052,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3163,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3274,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3385,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3472,7 +3496,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3583,7 +3607,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3694,7 +3718,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3738,13 +3762,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3833,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3849,13 +3877,695 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1237,24 +1237,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1950,10 +1950,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2053,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2164,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2242,12 +2250,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq42，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2275,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2283,10 +2291,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq39（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2386,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2719,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2854,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3076,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3187,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3274,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3385,7 +3409,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3496,7 +3520,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3607,7 +3631,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3718,7 +3742,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3833,7 +3857,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3948,7 +3972,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4063,7 +4087,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4131,7 +4155,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4174,7 +4198,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4188,7 +4212,7 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4285,7 +4309,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4334,12 +4358,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4381,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4400,7 +4424,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4414,7 +4438,7 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4511,7 +4535,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4560,12 +4584,234 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>157.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1687,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1764,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1881,7 +1889,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1922,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq41推进至seq56，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2008,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2100,7 +2108,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2111,7 +2119,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2211,7 +2219,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2222,7 +2230,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2263,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq42，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq60，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2283,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2349,7 +2357,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2449,7 +2457,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2460,7 +2468,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2488,32 +2496,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2521,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2545,33 +2557,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2671,7 +2687,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2682,7 +2698,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2793,7 +2809,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2893,7 +2909,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2904,7 +2920,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2981,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3015,7 +3031,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3092,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3126,7 +3142,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3203,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3237,7 +3253,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3314,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3348,7 +3364,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3425,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3459,7 +3475,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3536,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3570,7 +3586,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3647,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3681,7 +3697,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3758,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3796,7 +3812,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3873,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3911,7 +3927,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3988,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4103,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4137,7 +4153,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4214,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4248,7 +4264,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4325,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4363,7 +4379,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4440,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4474,7 +4490,7 @@
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4551,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4589,7 +4605,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4666,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4700,7 +4716,7 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4777,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4805,13 +4821,909 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr"/>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>—/27</t>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,32 +2726,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2759,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2783,33 +2787,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2948,32 +2956,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2981,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3005,17 +3017,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3025,13 +3037,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3075,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3092,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3116,33 +3136,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3170,32 +3194,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3203,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3227,33 +3255,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3281,32 +3313,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3314,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3338,17 +3374,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3358,13 +3394,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3392,32 +3432,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3425,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3449,17 +3493,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3469,13 +3513,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3503,32 +3551,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3536,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3560,33 +3612,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3686,7 +3742,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3725,32 +3781,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3758,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3782,17 +3842,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3802,17 +3862,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3955,32 +4015,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3988,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4012,32 +4076,32 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4103,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4142,7 +4206,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4181,12 +4245,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq60，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4214,18 +4278,30 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
           <t>10:11</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:26</t>
@@ -4325,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4379,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4551,7 +4627,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4605,7 +4681,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4742,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4705,7 +4781,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4777,7 +4853,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4831,7 +4907,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4968,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5003,7 +5079,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5114,7 +5190,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5225,7 +5301,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5336,7 +5412,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5390,7 +5466,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5527,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5562,7 +5638,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5620,22 +5696,22 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5673,7 +5749,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5717,11 +5793,919 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr"/>
-      <c r="AC46" s="2" t="inlineStr">
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,13 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,13 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1897,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2008,7 +2016,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,18 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,13 +2236,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2357,7 +2373,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,13 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2587,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2698,7 +2718,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2817,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2928,7 +2948,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3151,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3166,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3285,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3642,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3753,7 +3773,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4025,24 +4045,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4052,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4101,12 +4121,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4217,7 +4237,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4360,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4388,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4401,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,17 +4449,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4445,17 +4469,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4483,32 +4507,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4516,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4540,17 +4568,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4560,13 +4588,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4594,32 +4626,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4627,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4651,37 +4687,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4709,32 +4745,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4742,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4766,17 +4806,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4786,13 +4826,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4820,32 +4864,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4853,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4877,17 +4925,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4897,17 +4945,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4968,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,7 +5066,7 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5046,32 +5094,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5079,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5103,33 +5155,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5157,32 +5213,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5190,7 +5250,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5214,17 +5274,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5234,13 +5294,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5268,32 +5332,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5301,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5325,17 +5393,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5345,13 +5413,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5466,7 +5538,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5577,7 +5649,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5710,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5677,7 +5749,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5688,7 +5760,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5803,7 +5875,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5914,7 +5986,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5975,7 +6047,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6014,7 +6086,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6029,7 +6101,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6162,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6144,7 +6216,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6277,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6259,7 +6331,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6392,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6370,7 +6442,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6503,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6481,7 +6553,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6614,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6591,12 +6663,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6729,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6701,13 +6773,806 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr"/>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>—/28</t>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,13 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,17 +2826,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2898,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2942,13 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,12 +3184,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3251,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,13 +3775,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4479,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4836,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,24 +5235,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5250,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5289,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5299,12 +5311,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5342,24 +5354,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5369,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5418,12 +5430,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5451,32 +5463,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5484,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,37 +5524,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5615,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5677,32 +5693,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5710,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5734,17 +5754,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5754,13 +5774,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5788,32 +5812,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5821,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5845,32 +5873,32 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5903,32 +5931,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5936,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5960,17 +5992,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5980,13 +6012,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6014,32 +6050,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6047,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6071,17 +6111,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6091,12 +6131,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6129,32 +6169,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6162,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6186,17 +6230,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6206,17 +6250,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6244,32 +6288,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6277,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6301,37 +6349,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6359,32 +6407,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6392,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6416,17 +6468,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6436,13 +6488,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6614,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6668,7 +6724,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6783,7 +6839,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6900,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6898,7 +6954,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6959,7 +7015,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7070,7 +7126,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7181,7 +7237,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7296,7 +7352,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7407,7 +7463,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7451,13 +7507,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7465,22 +7525,22 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7513,12 +7573,12 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7532,47 +7592,507 @@
       <c r="T61" s="2" t="inlineStr"/>
       <c r="U61" s="2" t="inlineStr">
         <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
           <t>13:45</t>
         </is>
       </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W61" s="2" t="inlineStr">
+      <c r="W62" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X61" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
+      <c r="Z62" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>9/29</t>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>150.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,18 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2246,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3780,12 +3788,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,14 +3897,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>150.5</t>
@@ -3904,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4128,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,18 +4246,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4610,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4731,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4833,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5067,7 +5079,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5143,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5197,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5316,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6141,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6272,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6298,24 +6310,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6325,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6374,12 +6386,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6417,24 +6429,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6444,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6493,12 +6505,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6526,32 +6538,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6559,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6583,33 +6599,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6637,32 +6657,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6670,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6694,17 +6718,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6714,17 +6738,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6752,32 +6776,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6785,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6809,37 +6837,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6867,32 +6895,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6900,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6924,17 +6956,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6944,17 +6976,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6982,12 +7014,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq53，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7015,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7023,10 +7055,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7093,32 +7141,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7126,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7150,33 +7202,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7291,7 +7347,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7463,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7517,7 +7573,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7632,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7747,7 +7803,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7864,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7862,7 +7918,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7972,12 +8028,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8092,7 +8148,693 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,13 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,14 +3072,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>155.0</t>
@@ -3083,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4261,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4384,7 +4388,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5090,7 +5094,7 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,7 +5203,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5209,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5556,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,7 +5670,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5677,7 +5681,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,17 +5790,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5915,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6153,7 +6157,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6391,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6629,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6867,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6905,24 +6909,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6932,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6981,12 +6985,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7023,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq53，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7047,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7117,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7151,24 +7155,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7227,12 +7231,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7260,32 +7264,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7293,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,17 +7325,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7337,7 +7345,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7347,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7375,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7408,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7432,17 +7444,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7452,13 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7502,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7519,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7543,17 +7563,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7563,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7601,32 +7621,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7634,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7658,17 +7682,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7678,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7918,7 +7942,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7979,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8033,7 +8057,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8148,7 +8172,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8263,7 +8287,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8348,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8378,7 +8402,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8493,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8578,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8608,7 +8632,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8718,12 +8742,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8755,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8779,12 +8803,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8834,7 +8858,455 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,14 +3310,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,14 +3548,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,14 +4135,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6147,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,14 +6261,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,17 +6623,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,14 +6737,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7631,12 +7631,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7740,32 +7740,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7773,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,17 +7801,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7817,17 +7821,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7855,32 +7859,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7888,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,17 +7920,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7932,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7970,32 +7978,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8003,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,17 +8039,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8047,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8085,32 +8097,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8118,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8142,17 +8158,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8162,17 +8178,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8200,32 +8216,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8233,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,17 +8277,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8277,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8315,32 +8335,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8348,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8372,17 +8396,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8392,17 +8416,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8578,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8632,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8808,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8919,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9030,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9141,7 +9165,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9203,22 +9227,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9251,12 +9275,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9300,13 +9324,1048 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr"/>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8345,24 +8345,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,17 +8411,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8454,32 +8454,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8487,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,17 +8515,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8531,7 +8535,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8569,32 +8573,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8602,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,17 +8634,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8646,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8684,32 +8692,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8717,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8741,17 +8753,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8761,12 +8773,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8799,12 +8811,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq33，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8832,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8840,10 +8852,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8943,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9165,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9280,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9395,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9506,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9645,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9736,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9851,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9966,7 +9990,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10081,7 +10105,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10196,7 +10220,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10311,7 +10335,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10365,7 +10389,582 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>148.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8345,19 +8345,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8583,24 +8583,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq33，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq43，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9156,32 +9156,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9189,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,17 +9217,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9233,17 +9237,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9419,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9530,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9645,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9760,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9875,7 +9879,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9990,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10105,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10335,7 +10339,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10389,7 +10393,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10454,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10565,7 +10569,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10680,7 +10684,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10795,7 +10799,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10910,7 +10914,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10959,12 +10963,357 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,18 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,17 +3076,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4864,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,18 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5631,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,13 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6023,7 +6035,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6103,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6157,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6276,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6514,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6752,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7182,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7301,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7476,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7593,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,7 +7709,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7777,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8545,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8664,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8816,7 +8828,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq43，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8844,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8934,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8967,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,33 +9007,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9166,24 +9186,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9193,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9232,17 +9252,17 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9275,32 +9295,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9308,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,32 +9356,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9390,32 +9414,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>10:11</t>
@@ -9423,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9447,17 +9475,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9467,13 +9495,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9588,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9616,32 +9648,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9649,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9673,17 +9709,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9693,17 +9729,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9818,7 +9854,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9918,7 +9954,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9933,7 +9969,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10109,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10163,7 +10199,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10339,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10393,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10508,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10684,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10738,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10853,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10950,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11029,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11083,7 +11119,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11180,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11198,7 +11234,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11295,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11317,6 +11353,696 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,22 +3786,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,17 +7357,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9436,12 +9436,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9767,32 +9767,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9800,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,37 +9828,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9882,32 +9886,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9915,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9939,17 +9947,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9959,12 +9967,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9997,32 +10005,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10030,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10054,32 +10066,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10112,32 +10124,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10145,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,17 +10185,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10189,17 +10205,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10342,32 +10358,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10375,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10399,37 +10419,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10544,7 +10564,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10572,32 +10592,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10605,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10629,17 +10653,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10649,17 +10673,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10835,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10889,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11065,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11119,7 +11143,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11234,7 +11258,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11410,7 +11434,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11525,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11640,7 +11664,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11755,7 +11779,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11817,7 +11841,7 @@
       <c r="A97" s="2" t="inlineStr"/>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -11827,7 +11851,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11870,7 +11894,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11884,7 +11908,7 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
@@ -11914,17 +11938,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11932,22 +11956,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11980,12 +12004,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11999,47 +12023,852 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>22/30</t>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8190,17 +8190,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,17 +9257,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10477,32 +10477,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10510,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10534,17 +10538,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10554,17 +10558,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10683,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10711,32 +10715,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10744,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,37 +10776,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10826,32 +10834,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10859,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10883,17 +10895,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10903,17 +10915,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10941,32 +10953,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10974,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10998,17 +11014,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11018,17 +11034,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11056,32 +11072,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11089,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11113,17 +11133,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11133,17 +11153,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11171,32 +11191,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11204,7 +11228,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11228,17 +11252,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11248,17 +11272,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11343,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11434,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11473,7 +11497,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11516,32 +11540,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11549,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11573,17 +11601,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11593,17 +11621,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11718,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11833,7 +11861,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11948,7 +11976,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12063,7 +12091,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12152,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12178,7 +12206,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12354,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12408,7 +12436,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12497,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12584,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12699,7 +12727,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12753,7 +12781,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12842,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12872,6 +12900,236 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-12-浦东35路.xlsx
+++ b/data/export/2026-10-12-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,17 +7714,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9027,17 +9027,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9376,17 +9376,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9495,17 +9495,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,17 +9967,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11550,24 +11550,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11659,32 +11659,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11692,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,17 +11720,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11736,17 +11740,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11774,32 +11778,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11807,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11831,17 +11839,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11851,17 +11859,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12004,32 +12012,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12037,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12061,17 +12073,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12081,17 +12093,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12119,32 +12131,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12152,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12176,17 +12192,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12196,17 +12212,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12250,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq53，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12267,18 +12283,34 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
           <t>20:21</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12321,7 +12353,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12414,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12464,32 +12496,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>10:11</t>
@@ -12497,7 +12533,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12521,17 +12557,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12541,17 +12577,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12666,7 +12702,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12781,7 +12817,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12878,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12896,7 +12932,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12993,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13011,7 +13047,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13072,7 +13108,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
